--- a/primer_corte/talleres/etl_eda/EDA mercado tarjetas.xlsx
+++ b/primer_corte/talleres/etl_eda/EDA mercado tarjetas.xlsx
@@ -1,39 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57314\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AADCC43-F9D5-43E2-96B9-AA82A48B5CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="Inicio" sheetId="1" r:id="rId1"/>
-    <sheet name="Datos" sheetId="2" r:id="rId2"/>
-    <sheet name="Limpieza" sheetId="3" r:id="rId3"/>
-    <sheet name="Univariado" sheetId="4" r:id="rId4"/>
-    <sheet name="Bivariado" sheetId="5" r:id="rId5"/>
-    <sheet name="Correlacion" sheetId="6" r:id="rId6"/>
-    <sheet name="Conclusiones" sheetId="7" r:id="rId7"/>
+    <sheet name="Inicio" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Datos" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Limpieza" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Univariado" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Bivariado" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Correlacion" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Conclusiones" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -42,289 +26,304 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
-  <si>
-    <t>EDA — Mercado de Tarjetas de Producto (versión Excel)</t>
-  </si>
-  <si>
-    <t>Acompaña a la guía de la actividad: mismo dataset de ejemplo, resuelto con fórmulas de Excel.</t>
-  </si>
-  <si>
-    <t>Mapa del libro</t>
-  </si>
-  <si>
-    <t>Datos</t>
-  </si>
-  <si>
-    <t>Registro crudo de ventas, tal como se recolecta en la actividad (con errores intencionales).</t>
-  </si>
-  <si>
-    <t>Limpieza</t>
-  </si>
-  <si>
-    <t>Corrige formato de precios, detecta duplicados y valores faltantes.</t>
-  </si>
-  <si>
-    <t>Univariado</t>
-  </si>
-  <si>
-    <t>Estadísticas descriptivas y conteo por categoría (Paso 3).</t>
-  </si>
-  <si>
-    <t>Bivariado</t>
-  </si>
-  <si>
-    <t>Precio promedio por categoría e ingresos por vendedor (Paso 4).</t>
-  </si>
-  <si>
-    <t>Correlacion</t>
-  </si>
-  <si>
-    <t>Correlación calificación vs precio de venta (Paso 5).</t>
-  </si>
-  <si>
-    <t>Conclusiones</t>
-  </si>
-  <si>
-    <t>Espacio para registrar hallazgos e hipótesis (Paso 6).</t>
-  </si>
-  <si>
-    <t>Leyenda de colores</t>
-  </si>
-  <si>
-    <t>Texto azul</t>
-  </si>
-  <si>
-    <t>Dato de entrada — puedes reemplazarlo por los datos reales de tu grupo.</t>
-  </si>
-  <si>
-    <t>Texto negro</t>
-  </si>
-  <si>
-    <t>Resultado calculado con fórmula — no editar directamente.</t>
-  </si>
-  <si>
-    <t>Celda amarilla</t>
-  </si>
-  <si>
-    <t>Espacio para que el estudiante complete.</t>
-  </si>
-  <si>
-    <t>id_venta</t>
-  </si>
-  <si>
-    <t>vendedor</t>
-  </si>
-  <si>
-    <t>comprador</t>
-  </si>
-  <si>
-    <t>producto</t>
-  </si>
-  <si>
-    <t>categoria</t>
-  </si>
-  <si>
-    <t>precio_lista</t>
-  </si>
-  <si>
-    <t>precio_venta</t>
-  </si>
-  <si>
-    <t>cantidad</t>
-  </si>
-  <si>
-    <t>calificacion</t>
-  </si>
-  <si>
-    <t>ronda</t>
-  </si>
-  <si>
-    <t>Grupo A</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>Termo Acero 500ml</t>
-  </si>
-  <si>
-    <t>Hogar</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>22000</t>
-  </si>
-  <si>
-    <t>Grupo B</t>
-  </si>
-  <si>
-    <t>Audífonos BT Mini</t>
-  </si>
-  <si>
-    <t>Tecnología</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>65000</t>
-  </si>
-  <si>
-    <t>Cuaderno Ecológico</t>
-  </si>
-  <si>
-    <t>Papelería</t>
-  </si>
-  <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>Powerbank 10000mAh</t>
-  </si>
-  <si>
-    <t>45000</t>
-  </si>
-  <si>
-    <t>Nota: F5 tiene formato de miles inconsistente · G6 falta el precio de venta · fila 7 es una venta duplicada de la fila 4.</t>
-  </si>
-  <si>
-    <t>precio_lista_limpio</t>
-  </si>
-  <si>
-    <t>precio_venta_limpio</t>
-  </si>
-  <si>
-    <t>clave</t>
-  </si>
-  <si>
-    <t>duplicado</t>
-  </si>
-  <si>
-    <t>valor_faltante</t>
-  </si>
-  <si>
-    <t>incluir_analisis</t>
-  </si>
-  <si>
-    <t>precio_venta_final</t>
-  </si>
-  <si>
-    <t>cantidad_final</t>
-  </si>
-  <si>
-    <t>calificacion_final</t>
-  </si>
-  <si>
-    <t>duplicado / valor_faltante = TRUE se excluyen automáticamente de precio_venta_final, cantidad_final y calificacion_final.</t>
-  </si>
-  <si>
-    <t>Estadísticas de precio_venta (sin duplicados ni faltantes)</t>
-  </si>
-  <si>
-    <t>Conteo</t>
-  </si>
-  <si>
-    <t>Promedio</t>
-  </si>
-  <si>
-    <t>Mínimo</t>
-  </si>
-  <si>
-    <t>Máximo</t>
-  </si>
-  <si>
-    <t>Desviación estándar</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>Mediana</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>Límite inferior outlier (Q1-1.5·RIC)</t>
-  </si>
-  <si>
-    <t>Límite superior outlier (Q3+1.5·RIC)</t>
-  </si>
-  <si>
-    <t>Categoría</t>
-  </si>
-  <si>
-    <t>Ventas (sin duplicados)</t>
-  </si>
-  <si>
-    <t>Nota: si tu dataset real tiene otras categorías, agrega filas aquí y ajusta el rango de la tabla/gráfico.</t>
-  </si>
-  <si>
-    <t>Precio promedio por categoría</t>
-  </si>
-  <si>
-    <t>Precio promedio</t>
-  </si>
-  <si>
-    <t>Ingresos por vendedor</t>
-  </si>
-  <si>
-    <t>Vendedor</t>
-  </si>
-  <si>
-    <t>Ingreso total</t>
-  </si>
-  <si>
-    <t>Dispersión cantidad vs precio_venta</t>
-  </si>
-  <si>
-    <t>Fuente: Limpieza!P2:P7 (cantidad_final) y Limpieza!O2:O7 (precio_venta_final).</t>
-  </si>
-  <si>
-    <t>Correlación calificación vs precio de venta</t>
-  </si>
-  <si>
-    <t>Coeficiente de correlación</t>
-  </si>
-  <si>
-    <t>Interpretación</t>
-  </si>
-  <si>
-    <t>Recuerda: correlación no implica causalidad.</t>
-  </si>
-  <si>
-    <t>Completa las celdas amarillas con tus propios hallazgos, apoyado en las hojas anteriores.</t>
-  </si>
-  <si>
-    <t>Ejemplo (ya resuelto)</t>
-  </si>
-  <si>
-    <t>La categoría Tecnología tiene el precio promedio más alto del mercado.</t>
-  </si>
-  <si>
-    <t>Hallazgo 1</t>
-  </si>
-  <si>
-    <t>Hallazgo 2</t>
-  </si>
-  <si>
-    <t>Hipótesis a validar</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="95">
+  <si>
+    <t xml:space="preserve">EDA — Mercado de Tarjetas de Producto (versión Excel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acompaña a la guía de la actividad: mismo dataset de ejemplo, resuelto con fórmulas de Excel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mapa del libro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registro crudo de ventas, tal como se recolecta en la actividad (con errores intencionales).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrige formato de precios, detecta duplicados y valores faltantes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Univariado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadísticas descriptivas y conteo por categoría (Paso 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bivariado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio promedio por categoría e ingresos por vendedor (Paso 4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correlacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correlación calificación vs precio de venta (Paso 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espacio para registrar hallazgos e hipótesis (Paso 6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leyenda de colores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texto azul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dato de entrada — puedes reemplazarlo por los datos reales de tu grupo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texto negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultado calculado con fórmula — no editar directamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celda amarilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espacio para que el estudiante complete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vendedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comprador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio_lista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio_venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cantidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ronda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo Acero 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hogar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audífonos BT Mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnología</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuaderno Ecológico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papelería</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powerbank 10000mAh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota: F5 tiene formato de miles inconsistente · G6 falta el precio de venta · fila 7 es una venta duplicada de la fila 4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio_lista_limpio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio_venta_limpio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duplicado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_faltante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incluir_analisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio_venta_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cantidad_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calificacion_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duplicado / valor_faltante = TRUE se excluyen automáticamente de precio_venta_final, cantidad_final y calificacion_final.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadísticas de precio_venta (sin duplicados ni faltantes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conteo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mínimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máximo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desviación estándar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Límite inferior outlier (Q1-1.5·RIC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Límite superior outlier (Q3+1.5·RIC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categoría</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ventas (sin duplicados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota: si tu dataset real tiene otras categorías, agrega filas aquí y ajusta el rango de la tabla/gráfico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio promedio por categoría</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio promedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingresos por vendedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispersión cantidad vs precio_venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente: Limpieza!P2:P7 (cantidad_final) y Limpieza!O2:O7 (precio_venta_final).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correlación calificación vs precio de venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coeficiente de correlación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuerda: correlación no implica causalidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completa las celdas amarillas con tus propios hallazgos, apoyado en las hojas anteriores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejemplo (ya resuelto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La categoría Tecnología tiene el precio promedio más alto del mercado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallazgo 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se detecto que en la base de datos cruda tiene inconsistencias (datos faltantes, errores de formato y registros duplicados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallazgo 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se nota una correlación positiva de (0.93) entre el precio de venta y la calificación del producto es decir en estos datos los productos más costosos tienden a recibir las valoraciones más altas por parte de los compradores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hipótesis a validar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el grupo de vendedores con mayores ingresos totales tiene ese resultado por vender productos con mayor precio y no por vender precisamente más cantidades </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+  </numFmts>
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,63 +332,107 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <i/>
+      <i val="true"/>
       <sz val="11"/>
       <color rgb="FF4B4A3E"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <i/>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -419,14 +462,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFC9BC9C"/>
       </left>
@@ -442,37 +485,121 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -531,31 +658,14 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF23261F"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -566,18 +676,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Ventas por categoría</a:t>
@@ -595,7 +704,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -624,33 +732,38 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -692,32 +805,20 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8D7B-4DE0-9777-88DFE31E720D}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="92993959"/>
-        <c:axId val="3501681"/>
+        <c:overlap val="0"/>
+        <c:axId val="62231882"/>
+        <c:axId val="27368757"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92993959"/>
+        <c:axId val="62231882"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -734,17 +835,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3501681"/>
+        <c:crossAx val="27368757"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -752,7 +853,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3501681"/>
+        <c:axId val="27368757"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -775,18 +876,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>N.º de ventas</a:t>
@@ -802,7 +902,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -819,17 +919,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92993959"/>
+        <c:crossAx val="62231882"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -854,20 +954,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -880,18 +979,12 @@
       <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -902,18 +995,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Precio promedio por categoría</a:t>
@@ -931,7 +1023,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -960,33 +1051,38 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1028,32 +1124,20 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1192-44D3-9E63-823E1A414EA8}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="57872651"/>
-        <c:axId val="58929925"/>
+        <c:overlap val="0"/>
+        <c:axId val="35450459"/>
+        <c:axId val="20510126"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57872651"/>
+        <c:axId val="35450459"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1070,17 +1154,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58929925"/>
+        <c:crossAx val="20510126"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1088,7 +1172,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58929925"/>
+        <c:axId val="20510126"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1104,7 +1188,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1121,17 +1205,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57872651"/>
+        <c:crossAx val="35450459"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1156,20 +1240,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1182,18 +1265,12 @@
       <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1204,18 +1281,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Ingresos por vendedor</a:t>
@@ -1233,7 +1309,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1262,33 +1337,38 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1330,32 +1410,20 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1784-4CC3-9619-A950EDBE4D24}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="29986643"/>
-        <c:axId val="67910225"/>
+        <c:overlap val="0"/>
+        <c:axId val="25381071"/>
+        <c:axId val="31803647"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29986643"/>
+        <c:axId val="25381071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1372,17 +1440,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67910225"/>
+        <c:crossAx val="31803647"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1390,7 +1458,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67910225"/>
+        <c:axId val="31803647"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1406,7 +1474,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1423,17 +1491,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29986643"/>
+        <c:crossAx val="25381071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1458,20 +1526,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1484,18 +1551,12 @@
       <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1506,18 +1567,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Cantidad vs precio de venta</a:t>
@@ -1535,7 +1595,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1543,9 +1602,20 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Ventas</c:v>
+            <c:strRef>
+              <c:f>"Ventas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ventas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
@@ -1558,33 +1628,36 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1592,10 +1665,11 @@
             </c:extLst>
           </c:dLbls>
           <c:xVal>
-            <c:strRef>
+            <c:numRef>
               <c:f>Limpieza!$P$2:$P$7</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1608,8 +1682,8 @@
                 <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
@@ -1629,35 +1703,16 @@
                 <c:pt idx="3">
                   <c:v>20000</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5A55-4FBD-8C14-B4DF5F1DAADB}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="35089968"/>
-        <c:axId val="6667385"/>
+        <c:axId val="37329163"/>
+        <c:axId val="59393350"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="35089968"/>
+        <c:axId val="37329163"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1680,18 +1735,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Cantidad</a:t>
@@ -1707,7 +1761,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1724,22 +1778,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6667385"/>
+        <c:crossAx val="59393350"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="6667385"/>
+        <c:axId val="59393350"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1762,18 +1816,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Precio de venta</a:t>
@@ -1789,7 +1842,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1806,17 +1859,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35089968"/>
+        <c:crossAx val="37329163"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1841,20 +1894,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1867,18 +1919,12 @@
       <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1889,18 +1935,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Calificación vs precio de venta</a:t>
@@ -1918,7 +1963,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1926,9 +1970,20 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Ventas</c:v>
+            <c:strRef>
+              <c:f>"Ventas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ventas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
@@ -1941,33 +1996,36 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1984,17 +2042,17 @@
               </a:ln>
             </c:spPr>
             <c:trendlineType val="linear"/>
+            <c:forward val="0"/>
+            <c:backward val="0"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
-            <c:strRef>
+            <c:numRef>
               <c:f>Limpieza!$Q$2:$Q$7</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -2007,8 +2065,8 @@
                 <c:pt idx="3">
                   <c:v>4</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
@@ -2028,35 +2086,16 @@
                 <c:pt idx="3">
                   <c:v>20000</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4942-4C98-A2E3-5060181C1A35}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="43552985"/>
-        <c:axId val="57868568"/>
+        <c:axId val="72925075"/>
+        <c:axId val="51921991"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="43552985"/>
+        <c:axId val="72925075"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2079,18 +2118,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Calificación</a:t>
@@ -2106,7 +2144,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2123,22 +2161,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57868568"/>
+        <c:crossAx val="51921991"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="57868568"/>
+        <c:axId val="51921991"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2161,18 +2199,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Precio de venta</a:t>
@@ -2188,7 +2225,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2205,17 +2242,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43552985"/>
+        <c:crossAx val="72925075"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2240,20 +2277,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2266,16 +2302,1091 @@
       <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -2285,24 +3396,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>39240</xdr:colOff>
+      <xdr:colOff>38880</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:rowOff>21600</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="4812840" y="190440"/>
+        <a:ext cx="4336920" cy="2879280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2316,7 +3421,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -2326,24 +3431,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>38880</xdr:colOff>
+      <xdr:colOff>38520</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:rowOff>21600</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="5735880" y="0"/>
+        <a:ext cx="4336920" cy="2879280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2362,24 +3461,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>38880</xdr:colOff>
+      <xdr:colOff>38520</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>22320</xdr:rowOff>
+      <xdr:rowOff>21960</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="5735880" y="3048120"/>
+        <a:ext cx="4336920" cy="2879280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2398,24 +3491,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>38880</xdr:colOff>
+      <xdr:colOff>38520</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:rowOff>21600</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="5735880" y="6095880"/>
+        <a:ext cx="4336920" cy="2879280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2429,7 +3516,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -2439,24 +3526,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>39240</xdr:colOff>
+      <xdr:colOff>38880</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:rowOff>21600</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="4702320" y="190440"/>
+        <a:ext cx="4336920" cy="2879280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2470,7 +3551,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2512,12 +3593,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2546,7 +3627,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2567,7 +3648,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2618,7 +3699,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2636,1237 +3717,1295 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="78" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="9" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="9" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="9" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="9" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="11">
+      <c r="G6" s="11"/>
+      <c r="H6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="9" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="12" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="26" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
-        <f>Datos!A2</f>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="n">
+        <f aca="false">Datos!A2</f>
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="str">
-        <f>Datos!B2</f>
+      <c r="B2" s="13" t="str">
+        <f aca="false">Datos!B2</f>
         <v>Grupo A</v>
       </c>
-      <c r="C2" s="15" t="str">
-        <f>Datos!C2</f>
+      <c r="C2" s="13" t="str">
+        <f aca="false">Datos!C2</f>
         <v>Grupo C</v>
       </c>
-      <c r="D2" s="15" t="str">
-        <f>Datos!D2</f>
+      <c r="D2" s="13" t="str">
+        <f aca="false">Datos!D2</f>
         <v>Termo Acero 500ml</v>
       </c>
-      <c r="E2" s="15" t="str">
-        <f>Datos!E2</f>
+      <c r="E2" s="13" t="str">
+        <f aca="false">Datos!E2</f>
         <v>Hogar</v>
       </c>
-      <c r="F2" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(Datos!F2,".","")),"")</f>
+      <c r="F2" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(Datos!F2,".","")),"")</f>
         <v>25000</v>
       </c>
-      <c r="G2" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G2,".",""),",",".")),"")</f>
+      <c r="G2" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G2,".",""),",",".")),"")</f>
         <v>22000</v>
       </c>
-      <c r="H2" s="15">
-        <f>Datos!H2</f>
+      <c r="H2" s="13" t="n">
+        <f aca="false">Datos!H2</f>
         <v>2</v>
       </c>
-      <c r="I2" s="15">
-        <f>Datos!I2</f>
+      <c r="I2" s="13" t="n">
+        <f aca="false">Datos!I2</f>
         <v>4</v>
       </c>
-      <c r="J2" s="15">
-        <f>Datos!J2</f>
+      <c r="J2" s="13" t="n">
+        <f aca="false">Datos!J2</f>
         <v>1</v>
       </c>
-      <c r="K2" s="15" t="str">
-        <f t="shared" ref="K2:K7" si="0">B2&amp;"|"&amp;D2&amp;"|"&amp;J2</f>
+      <c r="K2" s="13" t="str">
+        <f aca="false">B2&amp;"|"&amp;D2&amp;"|"&amp;J2</f>
         <v>Grupo A|Termo Acero 500ml|1</v>
       </c>
-      <c r="L2" s="15" t="b">
-        <f>COUNTIFS($K$2:K2,K2)&gt;1</f>
+      <c r="L2" s="14" t="b">
+        <f aca="false">COUNTIFS($K$2:K2,K2)&gt;1</f>
         <v>0</v>
       </c>
-      <c r="M2" s="15" t="b">
-        <f t="shared" ref="M2:M7" si="1">(G2="")</f>
+      <c r="M2" s="14" t="b">
+        <f aca="false">(G2="")</f>
         <v>0</v>
       </c>
-      <c r="N2" s="15" t="b">
-        <f>NOT(OR(L2,M2))</f>
+      <c r="N2" s="14" t="b">
+        <f aca="false">NOT(OR(L2,M2))</f>
         <v>1</v>
       </c>
-      <c r="O2" s="15">
-        <f t="shared" ref="O2:O7" si="2">IF(N2,G2,"")</f>
+      <c r="O2" s="13" t="n">
+        <f aca="false">IF(N2,G2,"")</f>
         <v>22000</v>
       </c>
-      <c r="P2" s="15">
-        <f t="shared" ref="P2:P7" si="3">IF(N2,H2,"")</f>
+      <c r="P2" s="13" t="n">
+        <f aca="false">IF(N2,H2,"")</f>
         <v>2</v>
       </c>
-      <c r="Q2" s="15">
-        <f t="shared" ref="Q2:Q7" si="4">IF(N2,I2,"")</f>
+      <c r="Q2" s="13" t="n">
+        <f aca="false">IF(N2,I2,"")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
-        <f>Datos!A3</f>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="n">
+        <f aca="false">Datos!A3</f>
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="str">
-        <f>Datos!B3</f>
+      <c r="B3" s="13" t="str">
+        <f aca="false">Datos!B3</f>
         <v>Grupo B</v>
       </c>
-      <c r="C3" s="15" t="str">
-        <f>Datos!C3</f>
+      <c r="C3" s="13" t="str">
+        <f aca="false">Datos!C3</f>
         <v>Grupo A</v>
       </c>
-      <c r="D3" s="15" t="str">
-        <f>Datos!D3</f>
+      <c r="D3" s="13" t="str">
+        <f aca="false">Datos!D3</f>
         <v>Audífonos BT Mini</v>
       </c>
-      <c r="E3" s="15" t="str">
-        <f>Datos!E3</f>
+      <c r="E3" s="13" t="str">
+        <f aca="false">Datos!E3</f>
         <v>Tecnología</v>
       </c>
-      <c r="F3" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(Datos!F3,".","")),"")</f>
+      <c r="F3" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(Datos!F3,".","")),"")</f>
         <v>60000</v>
       </c>
-      <c r="G3" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G3,".",""),",",".")),"")</f>
+      <c r="G3" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G3,".",""),",",".")),"")</f>
         <v>65000</v>
       </c>
-      <c r="H3" s="15">
-        <f>Datos!H3</f>
+      <c r="H3" s="13" t="n">
+        <f aca="false">Datos!H3</f>
         <v>1</v>
       </c>
-      <c r="I3" s="15">
-        <f>Datos!I3</f>
+      <c r="I3" s="13" t="n">
+        <f aca="false">Datos!I3</f>
         <v>5</v>
       </c>
-      <c r="J3" s="15">
-        <f>Datos!J3</f>
+      <c r="J3" s="13" t="n">
+        <f aca="false">Datos!J3</f>
         <v>1</v>
       </c>
-      <c r="K3" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="K3" s="13" t="str">
+        <f aca="false">B3&amp;"|"&amp;D3&amp;"|"&amp;J3</f>
         <v>Grupo B|Audífonos BT Mini|1</v>
       </c>
-      <c r="L3" s="15" t="b">
-        <f>COUNTIFS($K$2:K3,K3)&gt;1</f>
+      <c r="L3" s="14" t="b">
+        <f aca="false">COUNTIFS($K$2:K3,K3)&gt;1</f>
         <v>0</v>
       </c>
-      <c r="M3" s="15" t="b">
-        <f t="shared" si="1"/>
+      <c r="M3" s="14" t="b">
+        <f aca="false">(G3="")</f>
         <v>0</v>
       </c>
-      <c r="N3" s="15" t="b">
-        <f t="shared" ref="N2:N7" si="5">NOT(OR(L3,M3))</f>
+      <c r="N3" s="14" t="b">
+        <f aca="false">NOT(OR(L3,M3))</f>
         <v>1</v>
       </c>
-      <c r="O3" s="15">
-        <f t="shared" si="2"/>
+      <c r="O3" s="13" t="n">
+        <f aca="false">IF(N3,G3,"")</f>
         <v>65000</v>
       </c>
-      <c r="P3" s="15">
-        <f t="shared" si="3"/>
+      <c r="P3" s="13" t="n">
+        <f aca="false">IF(N3,H3,"")</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="15">
-        <f t="shared" si="4"/>
+      <c r="Q3" s="13" t="n">
+        <f aca="false">IF(N3,I3,"")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
-        <f>Datos!A4</f>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="n">
+        <f aca="false">Datos!A4</f>
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="str">
-        <f>Datos!B4</f>
+      <c r="B4" s="13" t="str">
+        <f aca="false">Datos!B4</f>
         <v>Grupo C</v>
       </c>
-      <c r="C4" s="15" t="str">
-        <f>Datos!C4</f>
+      <c r="C4" s="13" t="str">
+        <f aca="false">Datos!C4</f>
         <v>Grupo B</v>
       </c>
-      <c r="D4" s="15" t="str">
-        <f>Datos!D4</f>
+      <c r="D4" s="13" t="str">
+        <f aca="false">Datos!D4</f>
         <v>Cuaderno Ecológico</v>
       </c>
-      <c r="E4" s="15" t="str">
-        <f>Datos!E4</f>
+      <c r="E4" s="13" t="str">
+        <f aca="false">Datos!E4</f>
         <v>Papelería</v>
       </c>
-      <c r="F4" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(Datos!F4,".","")),"")</f>
+      <c r="F4" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(Datos!F4,".","")),"")</f>
         <v>8000</v>
       </c>
-      <c r="G4" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G4,".",""),",",".")),"")</f>
+      <c r="G4" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G4,".",""),",",".")),"")</f>
         <v>8000</v>
       </c>
-      <c r="H4" s="15">
-        <f>Datos!H4</f>
+      <c r="H4" s="13" t="n">
+        <f aca="false">Datos!H4</f>
         <v>3</v>
       </c>
-      <c r="I4" s="15">
-        <f>Datos!I4</f>
+      <c r="I4" s="13" t="n">
+        <f aca="false">Datos!I4</f>
         <v>3</v>
       </c>
-      <c r="J4" s="15">
-        <f>Datos!J4</f>
+      <c r="J4" s="13" t="n">
+        <f aca="false">Datos!J4</f>
         <v>1</v>
       </c>
-      <c r="K4" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="K4" s="13" t="str">
+        <f aca="false">B4&amp;"|"&amp;D4&amp;"|"&amp;J4</f>
         <v>Grupo C|Cuaderno Ecológico|1</v>
       </c>
-      <c r="L4" s="15" t="b">
-        <f>COUNTIFS($K$2:K4,K4)&gt;1</f>
+      <c r="L4" s="14" t="b">
+        <f aca="false">COUNTIFS($K$2:K4,K4)&gt;1</f>
         <v>0</v>
       </c>
-      <c r="M4" s="15" t="b">
-        <f t="shared" si="1"/>
+      <c r="M4" s="14" t="b">
+        <f aca="false">(G4="")</f>
         <v>0</v>
       </c>
-      <c r="N4" s="15" t="b">
-        <f t="shared" si="5"/>
+      <c r="N4" s="14" t="b">
+        <f aca="false">NOT(OR(L4,M4))</f>
         <v>1</v>
       </c>
-      <c r="O4" s="15">
-        <f t="shared" si="2"/>
+      <c r="O4" s="13" t="n">
+        <f aca="false">IF(N4,G4,"")</f>
         <v>8000</v>
       </c>
-      <c r="P4" s="15">
-        <f t="shared" si="3"/>
+      <c r="P4" s="13" t="n">
+        <f aca="false">IF(N4,H4,"")</f>
         <v>3</v>
       </c>
-      <c r="Q4" s="15">
-        <f t="shared" si="4"/>
+      <c r="Q4" s="13" t="n">
+        <f aca="false">IF(N4,I4,"")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
-        <f>Datos!A5</f>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
+        <f aca="false">Datos!A5</f>
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="str">
-        <f>Datos!B5</f>
+      <c r="B5" s="13" t="str">
+        <f aca="false">Datos!B5</f>
         <v>Grupo A</v>
       </c>
-      <c r="C5" s="15" t="str">
-        <f>Datos!C5</f>
+      <c r="C5" s="13" t="str">
+        <f aca="false">Datos!C5</f>
         <v>Grupo B</v>
       </c>
-      <c r="D5" s="15" t="str">
-        <f>Datos!D5</f>
+      <c r="D5" s="13" t="str">
+        <f aca="false">Datos!D5</f>
         <v>Termo Acero 500ml</v>
       </c>
-      <c r="E5" s="15" t="str">
-        <f>Datos!E5</f>
+      <c r="E5" s="13" t="str">
+        <f aca="false">Datos!E5</f>
         <v>Hogar</v>
       </c>
-      <c r="F5" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(Datos!F5,".","")),"")</f>
+      <c r="F5" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(Datos!F5,".","")),"")</f>
         <v>25000</v>
       </c>
-      <c r="G5" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G5,".",""),",",".")),"")</f>
+      <c r="G5" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G5,".",""),",",".")),"")</f>
         <v>20000</v>
       </c>
-      <c r="H5" s="15">
-        <f>Datos!H5</f>
+      <c r="H5" s="13" t="n">
+        <f aca="false">Datos!H5</f>
         <v>1</v>
       </c>
-      <c r="I5" s="15">
-        <f>Datos!I5</f>
+      <c r="I5" s="13" t="n">
+        <f aca="false">Datos!I5</f>
         <v>4</v>
       </c>
-      <c r="J5" s="15">
-        <f>Datos!J5</f>
+      <c r="J5" s="13" t="n">
+        <f aca="false">Datos!J5</f>
         <v>2</v>
       </c>
-      <c r="K5" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="K5" s="13" t="str">
+        <f aca="false">B5&amp;"|"&amp;D5&amp;"|"&amp;J5</f>
         <v>Grupo A|Termo Acero 500ml|2</v>
       </c>
-      <c r="L5" s="15" t="b">
-        <f>COUNTIFS($K$2:K5,K5)&gt;1</f>
+      <c r="L5" s="14" t="b">
+        <f aca="false">COUNTIFS($K$2:K5,K5)&gt;1</f>
         <v>0</v>
       </c>
-      <c r="M5" s="15" t="b">
-        <f t="shared" si="1"/>
+      <c r="M5" s="14" t="b">
+        <f aca="false">(G5="")</f>
         <v>0</v>
       </c>
-      <c r="N5" s="15" t="b">
-        <f t="shared" si="5"/>
+      <c r="N5" s="14" t="b">
+        <f aca="false">NOT(OR(L5,M5))</f>
         <v>1</v>
       </c>
-      <c r="O5" s="15">
-        <f t="shared" si="2"/>
+      <c r="O5" s="13" t="n">
+        <f aca="false">IF(N5,G5,"")</f>
         <v>20000</v>
       </c>
-      <c r="P5" s="15">
-        <f t="shared" si="3"/>
+      <c r="P5" s="13" t="n">
+        <f aca="false">IF(N5,H5,"")</f>
         <v>1</v>
       </c>
-      <c r="Q5" s="15">
-        <f t="shared" si="4"/>
+      <c r="Q5" s="13" t="n">
+        <f aca="false">IF(N5,I5,"")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
-        <f>Datos!A6</f>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="n">
+        <f aca="false">Datos!A6</f>
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="str">
-        <f>Datos!B6</f>
+      <c r="B6" s="13" t="str">
+        <f aca="false">Datos!B6</f>
         <v>Grupo B</v>
       </c>
-      <c r="C6" s="15" t="str">
-        <f>Datos!C6</f>
+      <c r="C6" s="13" t="str">
+        <f aca="false">Datos!C6</f>
         <v>Grupo C</v>
       </c>
-      <c r="D6" s="15" t="str">
-        <f>Datos!D6</f>
+      <c r="D6" s="13" t="str">
+        <f aca="false">Datos!D6</f>
         <v>Powerbank 10000mAh</v>
       </c>
-      <c r="E6" s="15" t="str">
-        <f>Datos!E6</f>
+      <c r="E6" s="13" t="str">
+        <f aca="false">Datos!E6</f>
         <v>Tecnología</v>
       </c>
-      <c r="F6" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(Datos!F6,".","")),"")</f>
+      <c r="F6" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(Datos!F6,".","")),"")</f>
         <v>45000</v>
       </c>
-      <c r="G6" s="15" t="str">
-        <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G6,".",""),",",".")),"")</f>
+      <c r="G6" s="13" t="str">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G6,".",""),",",".")),"")</f>
         <v/>
       </c>
-      <c r="H6" s="15">
-        <f>Datos!H6</f>
+      <c r="H6" s="13" t="n">
+        <f aca="false">Datos!H6</f>
         <v>1</v>
       </c>
-      <c r="I6" s="15">
-        <f>Datos!I6</f>
+      <c r="I6" s="13" t="n">
+        <f aca="false">Datos!I6</f>
         <v>4</v>
       </c>
-      <c r="J6" s="15">
-        <f>Datos!J6</f>
+      <c r="J6" s="13" t="n">
+        <f aca="false">Datos!J6</f>
         <v>2</v>
       </c>
-      <c r="K6" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="K6" s="13" t="str">
+        <f aca="false">B6&amp;"|"&amp;D6&amp;"|"&amp;J6</f>
         <v>Grupo B|Powerbank 10000mAh|2</v>
       </c>
-      <c r="L6" s="15" t="b">
-        <f>COUNTIFS($K$2:K6,K6)&gt;1</f>
+      <c r="L6" s="14" t="b">
+        <f aca="false">COUNTIFS($K$2:K6,K6)&gt;1</f>
         <v>0</v>
       </c>
-      <c r="M6" s="15" t="b">
-        <f>(G6="")</f>
+      <c r="M6" s="14" t="b">
+        <f aca="false">(G6="")</f>
         <v>1</v>
       </c>
-      <c r="N6" s="15" t="b">
-        <f t="shared" si="5"/>
+      <c r="N6" s="14" t="b">
+        <f aca="false">NOT(OR(L6,M6))</f>
         <v>0</v>
       </c>
-      <c r="O6" s="15" t="str">
-        <f t="shared" si="2"/>
+      <c r="O6" s="13" t="str">
+        <f aca="false">IF(N6,G6,"")</f>
         <v/>
       </c>
-      <c r="P6" s="15" t="str">
-        <f t="shared" si="3"/>
+      <c r="P6" s="13" t="str">
+        <f aca="false">IF(N6,H6,"")</f>
         <v/>
       </c>
-      <c r="Q6" s="15" t="str">
-        <f t="shared" si="4"/>
+      <c r="Q6" s="13" t="str">
+        <f aca="false">IF(N6,I6,"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
-        <f>Datos!A7</f>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
+        <f aca="false">Datos!A7</f>
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="str">
-        <f>Datos!B7</f>
+      <c r="B7" s="13" t="str">
+        <f aca="false">Datos!B7</f>
         <v>Grupo C</v>
       </c>
-      <c r="C7" s="15" t="str">
-        <f>Datos!C7</f>
+      <c r="C7" s="13" t="str">
+        <f aca="false">Datos!C7</f>
         <v>Grupo B</v>
       </c>
-      <c r="D7" s="15" t="str">
-        <f>Datos!D7</f>
+      <c r="D7" s="13" t="str">
+        <f aca="false">Datos!D7</f>
         <v>Cuaderno Ecológico</v>
       </c>
-      <c r="E7" s="15" t="str">
-        <f>Datos!E7</f>
+      <c r="E7" s="13" t="str">
+        <f aca="false">Datos!E7</f>
         <v>Papelería</v>
       </c>
-      <c r="F7" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(Datos!F7,".","")),"")</f>
+      <c r="F7" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(Datos!F7,".","")),"")</f>
         <v>8000</v>
       </c>
-      <c r="G7" s="15">
-        <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G7,".",""),",",".")),"")</f>
+      <c r="G7" s="13" t="n">
+        <f aca="false">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Datos!G7,".",""),",",".")),"")</f>
         <v>8000</v>
       </c>
-      <c r="H7" s="15">
-        <f>Datos!H7</f>
+      <c r="H7" s="13" t="n">
+        <f aca="false">Datos!H7</f>
         <v>3</v>
       </c>
-      <c r="I7" s="15">
-        <f>Datos!I7</f>
+      <c r="I7" s="13" t="n">
+        <f aca="false">Datos!I7</f>
         <v>3</v>
       </c>
-      <c r="J7" s="15">
-        <f>Datos!J7</f>
+      <c r="J7" s="13" t="n">
+        <f aca="false">Datos!J7</f>
         <v>1</v>
       </c>
-      <c r="K7" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="K7" s="13" t="str">
+        <f aca="false">B7&amp;"|"&amp;D7&amp;"|"&amp;J7</f>
         <v>Grupo C|Cuaderno Ecológico|1</v>
       </c>
-      <c r="L7" s="15" t="b">
-        <f>COUNTIFS($K$2:K7,K7)&gt;1</f>
+      <c r="L7" s="14" t="b">
+        <f aca="false">COUNTIFS($K$2:K7,K7)&gt;1</f>
         <v>1</v>
       </c>
-      <c r="M7" s="15" t="b">
-        <f t="shared" si="1"/>
+      <c r="M7" s="14" t="b">
+        <f aca="false">(G7="")</f>
         <v>0</v>
       </c>
-      <c r="N7" s="15" t="b">
-        <f t="shared" si="5"/>
+      <c r="N7" s="14" t="b">
+        <f aca="false">NOT(OR(L7,M7))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="15" t="str">
-        <f t="shared" si="2"/>
+      <c r="O7" s="13" t="str">
+        <f aca="false">IF(N7,G7,"")</f>
         <v/>
       </c>
-      <c r="P7" s="15" t="str">
-        <f t="shared" si="3"/>
+      <c r="P7" s="13" t="str">
+        <f aca="false">IF(N7,H7,"")</f>
         <v/>
       </c>
-      <c r="Q7" s="15" t="str">
-        <f t="shared" si="4"/>
+      <c r="Q7" s="13" t="str">
+        <f aca="false">IF(N7,I7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="16">
-        <f>COUNT(Limpieza!$O$2:$O$7)</f>
+      <c r="B2" s="15" t="n">
+        <f aca="false">COUNT(Limpieza!$O$2:$O$7)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="16">
-        <f>AVERAGE(Limpieza!$O$2:$O$7)</f>
+      <c r="B3" s="15" t="n">
+        <f aca="false">AVERAGE(Limpieza!$O$2:$O$7)</f>
         <v>28750</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="16">
-        <f>MIN(Limpieza!$O$2:$O$7)</f>
+      <c r="B4" s="15" t="n">
+        <f aca="false">MIN(Limpieza!$O$2:$O$7)</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="16">
-        <f>MAX(Limpieza!$O$2:$O$7)</f>
+      <c r="B5" s="15" t="n">
+        <f aca="false">MAX(Limpieza!$O$2:$O$7)</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="16">
-        <f>STDEV(Limpieza!$O$2:$O$7)</f>
-        <v>24944.939366532843</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B6" s="15" t="n">
+        <f aca="false">STDEV(Limpieza!$O$2:$O$7)</f>
+        <v>24944.9393665328</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="16">
-        <f>QUARTILE(Limpieza!$O$2:$O$7,1)</f>
+      <c r="B7" s="15" t="n">
+        <f aca="false">QUARTILE(Limpieza!$O$2:$O$7,1)</f>
         <v>17000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="16">
-        <f>MEDIAN(Limpieza!$O$2:$O$7)</f>
+      <c r="B8" s="15" t="n">
+        <f aca="false">MEDIAN(Limpieza!$O$2:$O$7)</f>
         <v>21000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="16">
-        <f>QUARTILE(Limpieza!$O$2:$O$7,3)</f>
+      <c r="B9" s="15" t="n">
+        <f aca="false">QUARTILE(Limpieza!$O$2:$O$7,3)</f>
         <v>32750</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="16">
-        <f>B7-1.5*(B9-B7)</f>
+      <c r="B10" s="15" t="n">
+        <f aca="false">B7-1.5*(B9-B7)</f>
         <v>-6625</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="16">
-        <f>B9+1.5*(B9-B7)</f>
+      <c r="B11" s="15" t="n">
+        <f aca="false">B9+1.5*(B9-B7)</f>
         <v>56375</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="6">
-        <f>COUNTIFS(Limpieza!$E$2:$E$7,A14,Limpieza!$L$2:$L$7,FALSE())</f>
+      <c r="B14" s="4" t="n">
+        <f aca="false">COUNTIFS(Limpieza!$E$2:$E$7,A14,Limpieza!$L$2:$L$7,FALSE())</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="6">
-        <f>COUNTIFS(Limpieza!$E$2:$E$7,A15,Limpieza!$L$2:$L$7,FALSE())</f>
+      <c r="B15" s="4" t="n">
+        <f aca="false">COUNTIFS(Limpieza!$E$2:$E$7,A15,Limpieza!$L$2:$L$7,FALSE())</f>
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6">
-        <f>COUNTIFS(Limpieza!$E$2:$E$7,A16,Limpieza!$L$2:$L$7,FALSE())</f>
+      <c r="B16" s="4" t="n">
+        <f aca="false">COUNTIFS(Limpieza!$E$2:$E$7,A16,Limpieza!$L$2:$L$7,FALSE())</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="16">
-        <f>AVERAGEIF(Limpieza!$E$2:$E$7,A3,Limpieza!$O$2:$O$7)</f>
+      <c r="B3" s="15" t="n">
+        <f aca="false">AVERAGEIF(Limpieza!$E$2:$E$7,A3,Limpieza!$O$2:$O$7)</f>
         <v>21000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="16">
-        <f>AVERAGEIF(Limpieza!$E$2:$E$7,A4,Limpieza!$O$2:$O$7)</f>
+      <c r="B4" s="15" t="n">
+        <f aca="false">AVERAGEIF(Limpieza!$E$2:$E$7,A4,Limpieza!$O$2:$O$7)</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="16">
-        <f>AVERAGEIF(Limpieza!$E$2:$E$7,A5,Limpieza!$O$2:$O$7)</f>
+      <c r="B5" s="15" t="n">
+        <f aca="false">AVERAGEIF(Limpieza!$E$2:$E$7,A5,Limpieza!$O$2:$O$7)</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="16">
-        <f>SUMIF(Limpieza!$B$2:$B$7,A10,Limpieza!$O$2:$O$7)</f>
+      <c r="B10" s="15" t="n">
+        <f aca="false">SUMIF(Limpieza!$B$2:$B$7,A10,Limpieza!$O$2:$O$7)</f>
         <v>42000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="16">
-        <f>SUMIF(Limpieza!$B$2:$B$7,A11,Limpieza!$O$2:$O$7)</f>
+      <c r="B11" s="15" t="n">
+        <f aca="false">SUMIF(Limpieza!$B$2:$B$7,A11,Limpieza!$O$2:$O$7)</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="16">
-        <f>SUMIF(Limpieza!$B$2:$B$7,A12,Limpieza!$O$2:$O$7)</f>
+      <c r="B12" s="15" t="n">
+        <f aca="false">SUMIF(Limpieza!$B$2:$B$7,A12,Limpieza!$O$2:$O$7)</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="17">
-        <f>CORREL(Limpieza!$Q$2:$Q$7,Limpieza!$O$2:$O$7)</f>
-        <v>0.93286065820871011</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B3" s="16" t="n">
+        <f aca="false">CORREL(Limpieza!$Q$2:$Q$7,Limpieza!$O$2:$O$7)</f>
+        <v>0.93286065820871</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="6" t="str">
-        <f>IF(ABS(B3)&gt;=0.7,"Correlación fuerte",IF(ABS(B3)&gt;=0.3,"Correlación moderada","Correlación débil"))&amp;IF(B3&gt;=0," positiva."," negativa.")</f>
+      <c r="B4" s="4" t="str">
+        <f aca="false">IF(ABS(B3)&gt;=0.7,"Correlación fuerte",IF(ABS(B3)&gt;=0.3,"Correlación moderada","Correlación débil"))&amp;IF(B3&gt;=0," positiva."," negativa.")</f>
         <v>Correlación fuerte positiva.</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>85</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="6" width="16" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="124.52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B6" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="B8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3875,7 +5014,12 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B10:F10"/>
   </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>